--- a/data/trans_orig/P19C03-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P19C03-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2007 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>55581</t>
+          <t>55554</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82459</t>
+          <t>81751</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>69338</t>
+          <t>68072</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>97462</t>
+          <t>98704</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>130530</t>
+          <t>130891</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>171142</t>
+          <t>170114</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,32%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>109034</t>
+          <t>109742</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>135912</t>
+          <t>135939</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>103760</t>
+          <t>102518</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>131884</t>
+          <t>133150</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>221574</t>
+          <t>222602</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>262186</t>
+          <t>261825</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,67%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>120407</t>
+          <t>119622</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>157647</t>
+          <t>158252</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>117935</t>
+          <t>118420</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>155292</t>
+          <t>155637</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>247120</t>
+          <t>248806</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>300425</t>
+          <t>301791</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,51%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>251069</t>
+          <t>250464</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>288309</t>
+          <t>289094</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>285909</t>
+          <t>285564</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>323266</t>
+          <t>322781</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>549492</t>
+          <t>548126</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>602797</t>
+          <t>601111</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>70,73%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61233</t>
+          <t>61048</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>89956</t>
+          <t>90528</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>71425</t>
+          <t>72772</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>100919</t>
+          <t>102760</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>139962</t>
+          <t>139574</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>182535</t>
+          <t>181191</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,49%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>146581</t>
+          <t>146009</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>175304</t>
+          <t>175489</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>187887</t>
+          <t>186046</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>217381</t>
+          <t>216034</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>342808</t>
+          <t>344152</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>385381</t>
+          <t>385769</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,43%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69756</t>
+          <t>69355</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>100558</t>
+          <t>99574</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>81236</t>
+          <t>81142</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>111316</t>
+          <t>113422</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>157881</t>
+          <t>157700</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>200919</t>
+          <t>201655</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,56%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>166973</t>
+          <t>167957</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>197775</t>
+          <t>198176</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>188218</t>
+          <t>186112</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>218298</t>
+          <t>218392</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>366146</t>
+          <t>365410</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>409184</t>
+          <t>409365</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,19%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37068</t>
+          <t>37268</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60922</t>
+          <t>60655</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37852</t>
+          <t>36495</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61772</t>
+          <t>62007</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>81231</t>
+          <t>81380</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>113862</t>
+          <t>115050</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,43%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>109356</t>
+          <t>109623</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>133210</t>
+          <t>133010</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>112134</t>
+          <t>111899</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>136054</t>
+          <t>137411</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>230322</t>
+          <t>229134</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>262953</t>
+          <t>262804</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,36%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42292</t>
+          <t>43580</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67462</t>
+          <t>67433</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41278</t>
+          <t>42153</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>66791</t>
+          <t>66403</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>91481</t>
+          <t>90788</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>127297</t>
+          <t>124358</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>31,58%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>121808</t>
+          <t>121837</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>146978</t>
+          <t>145690</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>137697</t>
+          <t>138085</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>163210</t>
+          <t>162335</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>266461</t>
+          <t>269400</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>302277</t>
+          <t>302970</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,94%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>133590</t>
+          <t>134196</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>175119</t>
+          <t>176500</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>148075</t>
+          <t>144729</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>191061</t>
+          <t>189091</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>293071</t>
+          <t>293446</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>354927</t>
+          <t>351038</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>34,97%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>289206</t>
+          <t>287825</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>330735</t>
+          <t>330129</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>348307</t>
+          <t>350277</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>391293</t>
+          <t>394639</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>648765</t>
+          <t>652654</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>710621</t>
+          <t>710246</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,76%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>141828</t>
+          <t>140750</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>182541</t>
+          <t>183317</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>183352</t>
+          <t>183690</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>232556</t>
+          <t>231938</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>337979</t>
+          <t>338636</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>401030</t>
+          <t>402208</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,98%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>343011</t>
+          <t>342235</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>383724</t>
+          <t>384802</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>359856</t>
+          <t>360474</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>409060</t>
+          <t>408722</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>716933</t>
+          <t>715755</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>779984</t>
+          <t>779327</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>69,71%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>738000</t>
+          <t>738252</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>835283</t>
+          <t>831122</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>825485</t>
+          <t>832173</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>928483</t>
+          <t>926843</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1595910</t>
+          <t>1600758</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1728616</t>
+          <t>1731109</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,32%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1618418</t>
+          <t>1622579</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1715701</t>
+          <t>1715449</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1812454</t>
+          <t>1814094</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1915452</t>
+          <t>1908764</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3466022</t>
+          <t>3463529</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3598728</t>
+          <t>3593880</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,18%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2012 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35052</t>
+          <t>36195</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59992</t>
+          <t>60288</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51825</t>
+          <t>50662</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>81476</t>
+          <t>80638</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>92787</t>
+          <t>92927</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>131879</t>
+          <t>133330</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,68%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>190568</t>
+          <t>190272</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>215508</t>
+          <t>214365</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>167763</t>
+          <t>168601</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>197414</t>
+          <t>198577</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>367921</t>
+          <t>366470</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>407013</t>
+          <t>406873</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,41%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>104910</t>
+          <t>105875</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>142082</t>
+          <t>143740</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>115539</t>
+          <t>114994</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>156195</t>
+          <t>154533</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>229478</t>
+          <t>232809</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>287102</t>
+          <t>287378</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,08%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>264248</t>
+          <t>262590</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>301420</t>
+          <t>300455</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>280633</t>
+          <t>282295</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>321289</t>
+          <t>321834</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>556055</t>
+          <t>555779</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>613679</t>
+          <t>610348</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>72,39%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81520</t>
+          <t>80930</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>112622</t>
+          <t>111783</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>71816</t>
+          <t>72275</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104873</t>
+          <t>103740</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>160338</t>
+          <t>163259</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>207990</t>
+          <t>208357</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,48%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>181042</t>
+          <t>181881</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>212144</t>
+          <t>212734</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>223879</t>
+          <t>225012</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>256936</t>
+          <t>256477</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>414426</t>
+          <t>414059</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>462078</t>
+          <t>459157</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>73,77%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88247</t>
+          <t>89428</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>121827</t>
+          <t>124350</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70528</t>
+          <t>68726</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>102302</t>
+          <t>102337</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>166899</t>
+          <t>168171</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>217706</t>
+          <t>215794</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>32,9%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>191250</t>
+          <t>188727</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>224830</t>
+          <t>223649</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>240513</t>
+          <t>240478</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>272287</t>
+          <t>274089</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>438185</t>
+          <t>440097</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>488992</t>
+          <t>487720</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,36%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48303</t>
+          <t>47319</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>74835</t>
+          <t>74513</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45610</t>
+          <t>45745</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72156</t>
+          <t>71817</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>101348</t>
+          <t>100440</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>137858</t>
+          <t>138092</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,72%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>117223</t>
+          <t>117545</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>143755</t>
+          <t>144739</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>122426</t>
+          <t>122765</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>148972</t>
+          <t>148837</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>248782</t>
+          <t>248548</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>285292</t>
+          <t>286200</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>74,02%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51032</t>
+          <t>51029</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81983</t>
+          <t>80633</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>57104</t>
+          <t>57177</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>85244</t>
+          <t>85881</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>116072</t>
+          <t>117848</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>156031</t>
+          <t>157843</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,66%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>167990</t>
+          <t>169340</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>198941</t>
+          <t>198944</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>179586</t>
+          <t>178949</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>207726</t>
+          <t>207653</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>358772</t>
+          <t>356960</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>398731</t>
+          <t>396955</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,11%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>149704</t>
+          <t>150075</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>197334</t>
+          <t>196057</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>149291</t>
+          <t>148913</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>197330</t>
+          <t>197500</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>310218</t>
+          <t>314096</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>376587</t>
+          <t>378964</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,65%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>374970</t>
+          <t>376247</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>422600</t>
+          <t>422229</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>427814</t>
+          <t>427644</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>475853</t>
+          <t>476231</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>820861</t>
+          <t>818484</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>887230</t>
+          <t>883352</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>73,77%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>178664</t>
+          <t>179170</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>227558</t>
+          <t>227334</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>211659</t>
+          <t>212248</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>264104</t>
+          <t>261683</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>403445</t>
+          <t>402365</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>472697</t>
+          <t>473401</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,43%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>406347</t>
+          <t>406571</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>455241</t>
+          <t>454735</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>438190</t>
+          <t>440611</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>490635</t>
+          <t>490046</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>863502</t>
+          <t>862798</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>932754</t>
+          <t>933834</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,89%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>819942</t>
+          <t>823239</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>925148</t>
+          <t>931331</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>850603</t>
+          <t>862414</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>961140</t>
+          <t>965794</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1714774</t>
+          <t>1714290</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1865452</t>
+          <t>1857413</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,67%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1986723</t>
+          <t>1980540</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2091929</t>
+          <t>2088632</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2183343</t>
+          <t>2178689</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2293880</t>
+          <t>2282069</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4190903</t>
+          <t>4198942</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4341581</t>
+          <t>4342065</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53444</t>
+          <t>54706</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82922</t>
+          <t>84334</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42779</t>
+          <t>42349</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67929</t>
+          <t>68352</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>103915</t>
+          <t>103819</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>140891</t>
+          <t>142971</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>29,09%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>162296</t>
+          <t>160884</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>191774</t>
+          <t>190512</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>178405</t>
+          <t>177982</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>203555</t>
+          <t>203985</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>350660</t>
+          <t>348580</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>387636</t>
+          <t>387732</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,88%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>102599</t>
+          <t>97406</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>138027</t>
+          <t>136071</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87395</t>
+          <t>87766</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>122874</t>
+          <t>122548</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>200163</t>
+          <t>199472</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>250128</t>
+          <t>249932</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,04%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>225138</t>
+          <t>227094</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>260566</t>
+          <t>265759</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>270453</t>
+          <t>270779</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>305932</t>
+          <t>305561</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>506364</t>
+          <t>506560</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>556329</t>
+          <t>557020</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>73,63%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>66110</t>
+          <t>65398</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>94766</t>
+          <t>95764</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59855</t>
+          <t>59465</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89017</t>
+          <t>89247</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>135392</t>
+          <t>135254</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>178744</t>
+          <t>176332</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>195741</t>
+          <t>194743</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>224397</t>
+          <t>225109</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>218747</t>
+          <t>218517</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>247909</t>
+          <t>248299</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>419526</t>
+          <t>421938</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>462878</t>
+          <t>463016</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,39%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46423</t>
+          <t>46973</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75944</t>
+          <t>74295</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68970</t>
+          <t>69053</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101707</t>
+          <t>104922</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>124175</t>
+          <t>123636</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>166193</t>
+          <t>166116</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,47%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>254103</t>
+          <t>255752</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>283624</t>
+          <t>283074</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>247154</t>
+          <t>243939</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>279891</t>
+          <t>279808</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>512715</t>
+          <t>512792</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>554733</t>
+          <t>555272</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,79%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19783</t>
+          <t>19910</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38141</t>
+          <t>38426</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25816</t>
+          <t>26230</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45912</t>
+          <t>45679</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51193</t>
+          <t>49466</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78375</t>
+          <t>77175</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,15%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81081</t>
+          <t>80796</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>99439</t>
+          <t>99312</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>99588</t>
+          <t>99821</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>119684</t>
+          <t>119270</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>186347</t>
+          <t>187547</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>213529</t>
+          <t>215256</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>81,31%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40812</t>
+          <t>40169</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>65953</t>
+          <t>66223</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40312</t>
+          <t>41902</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65863</t>
+          <t>66569</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>87959</t>
+          <t>87820</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>123648</t>
+          <t>124717</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,94%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>167662</t>
+          <t>167392</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>192803</t>
+          <t>193446</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>181274</t>
+          <t>180568</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>206825</t>
+          <t>205235</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>357105</t>
+          <t>356036</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>392794</t>
+          <t>392933</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,73%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>137512</t>
+          <t>137167</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>178589</t>
+          <t>179736</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>139384</t>
+          <t>140158</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>181759</t>
+          <t>181739</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>290729</t>
+          <t>289606</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>351157</t>
+          <t>348521</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,5%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>263718</t>
+          <t>262571</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>304795</t>
+          <t>305140</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>305292</t>
+          <t>305312</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>347667</t>
+          <t>346893</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>578201</t>
+          <t>580837</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>638629</t>
+          <t>639752</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,84%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>146522</t>
+          <t>147318</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>190050</t>
+          <t>192066</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>166017</t>
+          <t>165414</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>212024</t>
+          <t>212512</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>322365</t>
+          <t>323788</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>386742</t>
+          <t>388244</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,16%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>450202</t>
+          <t>448186</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>493730</t>
+          <t>492934</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>479317</t>
+          <t>478829</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>525324</t>
+          <t>525927</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>944851</t>
+          <t>943349</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1009228</t>
+          <t>1007805</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>75,68%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>683521</t>
+          <t>692520</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>780111</t>
+          <t>783155</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>707216</t>
+          <t>707993</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>799085</t>
+          <t>804134</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1419039</t>
+          <t>1416417</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1551376</t>
+          <t>1558872</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,18%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1884222</t>
+          <t>1881178</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1980812</t>
+          <t>1971813</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2068230</t>
+          <t>2063181</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2160099</t>
+          <t>2159322</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3980272</t>
+          <t>3972776</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4112609</t>
+          <t>4115231</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,39%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2023 (tasa de respuesta: 99,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32667</t>
+          <t>31714</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59181</t>
+          <t>60131</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53135</t>
+          <t>53776</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>80426</t>
+          <t>79821</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>90959</t>
+          <t>90920</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>133446</t>
+          <t>132590</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,36%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>246249</t>
+          <t>245299</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>272763</t>
+          <t>273716</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>207181</t>
+          <t>207786</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>234472</t>
+          <t>233831</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>459591</t>
+          <t>460447</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>502078</t>
+          <t>502117</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,67%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>114334</t>
+          <t>113903</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>165010</t>
+          <t>170626</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>94653</t>
+          <t>92759</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>129324</t>
+          <t>129753</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>219613</t>
+          <t>216151</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>282419</t>
+          <t>280441</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,81%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>341974</t>
+          <t>336358</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>392650</t>
+          <t>393081</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>372224</t>
+          <t>371795</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>406895</t>
+          <t>408789</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>726113</t>
+          <t>728091</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>788919</t>
+          <t>792381</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,57%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41782</t>
+          <t>41162</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68706</t>
+          <t>68359</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35882</t>
+          <t>38335</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57076</t>
+          <t>59751</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>84676</t>
+          <t>85812</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>119993</t>
+          <t>120365</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,91%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>232486</t>
+          <t>232833</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>259410</t>
+          <t>260030</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>278199</t>
+          <t>275524</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>299393</t>
+          <t>296940</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>516474</t>
+          <t>516102</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>551791</t>
+          <t>550655</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,52%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42622</t>
+          <t>42432</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83762</t>
+          <t>81789</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62937</t>
+          <t>58776</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>189822</t>
+          <t>179504</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>114872</t>
+          <t>117555</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>239908</t>
+          <t>247720</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>31,61%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>226358</t>
+          <t>228331</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>267498</t>
+          <t>267688</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>283643</t>
+          <t>293961</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>410528</t>
+          <t>414689</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>543677</t>
+          <t>535865</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>668713</t>
+          <t>666030</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,0%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27996</t>
+          <t>28176</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45534</t>
+          <t>45685</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38334</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55119</t>
+          <t>53750</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>69431</t>
+          <t>71014</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>93788</t>
+          <t>93870</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,32%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>122895</t>
+          <t>122744</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>140433</t>
+          <t>140253</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>147173</t>
+          <t>148542</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>163777</t>
+          <t>163958</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>276933</t>
+          <t>276851</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>301290</t>
+          <t>299707</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>80,84%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46635</t>
+          <t>47102</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>73594</t>
+          <t>71132</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31161</t>
+          <t>30883</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49473</t>
+          <t>49913</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>82733</t>
+          <t>84036</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>116195</t>
+          <t>115025</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,0%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>180138</t>
+          <t>182600</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>207097</t>
+          <t>206630</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>196877</t>
+          <t>196437</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>215189</t>
+          <t>215467</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>383887</t>
+          <t>385057</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>417349</t>
+          <t>416046</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,2%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>116878</t>
+          <t>115528</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>163875</t>
+          <t>164467</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>59076</t>
+          <t>59144</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>180699</t>
+          <t>179755</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>160474</t>
+          <t>165850</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>323767</t>
+          <t>325307</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,79%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>435820</t>
+          <t>435228</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>482817</t>
+          <t>484167</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>647023</t>
+          <t>647967</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>768646</t>
+          <t>768578</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1103650</t>
+          <t>1102110</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1266943</t>
+          <t>1261567</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,38%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29310</t>
+          <t>31160</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>104101</t>
+          <t>102636</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>72816</t>
+          <t>72228</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>101109</t>
+          <t>99472</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>91155</t>
+          <t>96851</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>191804</t>
+          <t>190484</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>803441</t>
+          <t>804906</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>878232</t>
+          <t>876382</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>602815</t>
+          <t>604452</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>631108</t>
+          <t>631696</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1419663</t>
+          <t>1420983</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1520312</t>
+          <t>1514616</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>93,99%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>466080</t>
+          <t>462873</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>677159</t>
+          <t>672309</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>518144</t>
+          <t>520003</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>714249</t>
+          <t>711757</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1057834</t>
+          <t>1075093</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1341274</t>
+          <t>1342961</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2675966</t>
+          <t>2680816</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2887045</t>
+          <t>2890252</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2863935</t>
+          <t>2866427</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3060040</t>
+          <t>3058181</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5590035</t>
+          <t>5588348</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5873475</t>
+          <t>5856216</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,49%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C03-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P19C03-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>55554</t>
+          <t>55572</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>81751</t>
+          <t>82255</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>68072</t>
+          <t>67300</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>98704</t>
+          <t>95644</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>130891</t>
+          <t>132236</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>170114</t>
+          <t>171210</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>43,6%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>109742</t>
+          <t>109238</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>135939</t>
+          <t>135921</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>102518</t>
+          <t>105578</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>133150</t>
+          <t>133922</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>222602</t>
+          <t>221506</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>261825</t>
+          <t>260480</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,33%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>119622</t>
+          <t>117758</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>158252</t>
+          <t>158410</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>118420</t>
+          <t>115232</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>155637</t>
+          <t>154994</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>248806</t>
+          <t>248309</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>301791</t>
+          <t>305291</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,92%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>250464</t>
+          <t>250306</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>289094</t>
+          <t>290958</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>285564</t>
+          <t>286207</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>322781</t>
+          <t>325969</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>548126</t>
+          <t>544626</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>601111</t>
+          <t>601608</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>70,78%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61048</t>
+          <t>60415</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90528</t>
+          <t>89704</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72772</t>
+          <t>71234</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>102760</t>
+          <t>101535</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>139574</t>
+          <t>139982</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>181191</t>
+          <t>182618</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,76%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>146009</t>
+          <t>146833</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>175489</t>
+          <t>176122</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>186046</t>
+          <t>187271</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>216034</t>
+          <t>217572</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>344152</t>
+          <t>342725</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>385769</t>
+          <t>385361</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,35%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69355</t>
+          <t>68699</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>99574</t>
+          <t>99657</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>81142</t>
+          <t>80310</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>113422</t>
+          <t>112573</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>157700</t>
+          <t>158922</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>201655</t>
+          <t>202925</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,79%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>167957</t>
+          <t>167874</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>198176</t>
+          <t>198832</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>186112</t>
+          <t>186961</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>218392</t>
+          <t>219224</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>365410</t>
+          <t>364140</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>409365</t>
+          <t>408143</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>71,97%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37268</t>
+          <t>36916</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60655</t>
+          <t>60669</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36495</t>
+          <t>37244</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62007</t>
+          <t>61155</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>81380</t>
+          <t>82741</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>115050</t>
+          <t>113700</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,03%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>109623</t>
+          <t>109609</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>133010</t>
+          <t>133362</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>111899</t>
+          <t>112751</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>137411</t>
+          <t>136662</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>229134</t>
+          <t>230484</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>262804</t>
+          <t>261443</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>75,96%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43580</t>
+          <t>42848</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67433</t>
+          <t>66593</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,82 +2463,82 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>22,64%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>35,18%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>52931</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>41370</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>65586</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>25,88%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>20,23%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>32,07%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>107796</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>90677</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>125594</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>27,38%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>23,03%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>35,63%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>52931</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>42153</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>66403</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>25,88%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>20,61%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>32,47%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>107796</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>90788</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>124358</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>27,38%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>23,06%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,9%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>121837</t>
+          <t>122677</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>145690</t>
+          <t>146422</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,82 +2576,82 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>77,36%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>151557</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>138902</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>163118</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>74,12%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>67,93%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>79,77%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>285962</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>268164</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>303081</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>72,62%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>68,1%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
           <t>76,97%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>151557</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>138085</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>162335</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>74,12%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>67,53%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>79,39%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>285962</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>269400</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>302970</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>72,62%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>68,42%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>76,94%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>134196</t>
+          <t>134064</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>176500</t>
+          <t>176184</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>144729</t>
+          <t>148550</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>189091</t>
+          <t>191424</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>293446</t>
+          <t>294138</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>351038</t>
+          <t>356608</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,53%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>287825</t>
+          <t>288141</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>330129</t>
+          <t>330261</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>350277</t>
+          <t>347944</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>394639</t>
+          <t>390818</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>652654</t>
+          <t>647084</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>710246</t>
+          <t>709554</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,69%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>140750</t>
+          <t>140436</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>183317</t>
+          <t>183195</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>183690</t>
+          <t>184792</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>231938</t>
+          <t>232473</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>338636</t>
+          <t>338719</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>402208</t>
+          <t>402275</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>342235</t>
+          <t>342357</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>384802</t>
+          <t>385116</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>360474</t>
+          <t>359939</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>408722</t>
+          <t>407620</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>715755</t>
+          <t>715688</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>779327</t>
+          <t>779244</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,7%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>738252</t>
+          <t>736551</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>831122</t>
+          <t>833872</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>832173</t>
+          <t>826844</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>926843</t>
+          <t>928824</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1600758</t>
+          <t>1590088</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1731109</t>
+          <t>1727432</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,25%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1622579</t>
+          <t>1619829</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1715449</t>
+          <t>1717150</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1814094</t>
+          <t>1812113</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1908764</t>
+          <t>1914093</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3463529</t>
+          <t>3467206</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3593880</t>
+          <t>3604550</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,39%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36195</t>
+          <t>35718</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60288</t>
+          <t>61183</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50662</t>
+          <t>51236</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>80638</t>
+          <t>81080</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>92927</t>
+          <t>94161</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>133330</t>
+          <t>132120</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>190272</t>
+          <t>189377</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>214365</t>
+          <t>214842</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>168601</t>
+          <t>168159</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>198577</t>
+          <t>198003</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>366470</t>
+          <t>367680</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>406873</t>
+          <t>405639</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,16%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>105875</t>
+          <t>105795</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>143740</t>
+          <t>144320</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>114994</t>
+          <t>116782</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>154533</t>
+          <t>156764</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>232809</t>
+          <t>231036</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>287378</t>
+          <t>285316</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,84%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>262590</t>
+          <t>262010</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>300455</t>
+          <t>300535</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>282295</t>
+          <t>280064</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>321834</t>
+          <t>320046</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>555779</t>
+          <t>557841</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>610348</t>
+          <t>612121</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>72,6%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80930</t>
+          <t>80478</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>111783</t>
+          <t>113780</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72275</t>
+          <t>72655</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>103740</t>
+          <t>105482</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>163259</t>
+          <t>161498</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>208357</t>
+          <t>208732</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,54%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>181881</t>
+          <t>179884</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>212734</t>
+          <t>213186</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>225012</t>
+          <t>223270</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>256477</t>
+          <t>256097</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>414059</t>
+          <t>413684</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>459157</t>
+          <t>460918</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>74,05%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89428</t>
+          <t>89399</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>124350</t>
+          <t>123093</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68726</t>
+          <t>69747</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>102337</t>
+          <t>102719</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>168171</t>
+          <t>167382</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>215794</t>
+          <t>216252</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,97%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>188727</t>
+          <t>189984</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>223649</t>
+          <t>223678</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>240478</t>
+          <t>240096</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>274089</t>
+          <t>273068</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>440097</t>
+          <t>439639</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>487720</t>
+          <t>488509</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,48%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>47319</t>
+          <t>47400</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>74513</t>
+          <t>74299</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45745</t>
+          <t>46127</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71817</t>
+          <t>72994</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>100440</t>
+          <t>99598</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>138092</t>
+          <t>139510</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>36,08%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>117545</t>
+          <t>117759</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>144739</t>
+          <t>144658</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>122765</t>
+          <t>121588</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>148837</t>
+          <t>148455</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>248548</t>
+          <t>247130</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>286200</t>
+          <t>287042</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>74,24%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51029</t>
+          <t>53160</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80633</t>
+          <t>80102</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>57177</t>
+          <t>56282</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>85881</t>
+          <t>86360</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>117848</t>
+          <t>118078</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>157843</t>
+          <t>159338</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,95%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>169340</t>
+          <t>169871</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>198944</t>
+          <t>196813</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>178949</t>
+          <t>178470</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>207653</t>
+          <t>208548</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>356960</t>
+          <t>355465</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>396955</t>
+          <t>396725</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>77,06%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>150075</t>
+          <t>147431</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>196057</t>
+          <t>192354</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>148913</t>
+          <t>152093</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>197500</t>
+          <t>198438</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>314096</t>
+          <t>312044</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>378964</t>
+          <t>378735</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,63%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>376247</t>
+          <t>379950</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>422229</t>
+          <t>424873</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>427644</t>
+          <t>426706</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>476231</t>
+          <t>473051</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>818484</t>
+          <t>818713</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>883352</t>
+          <t>885404</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>73,94%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>179170</t>
+          <t>178232</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>227334</t>
+          <t>229654</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>212248</t>
+          <t>210651</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>261683</t>
+          <t>262531</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>402365</t>
+          <t>404246</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>473401</t>
+          <t>473040</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,4%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>406571</t>
+          <t>404251</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>454735</t>
+          <t>455673</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>440611</t>
+          <t>439763</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>490046</t>
+          <t>491643</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>862798</t>
+          <t>863159</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>933834</t>
+          <t>931953</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>69,75%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>823239</t>
+          <t>825376</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>931331</t>
+          <t>926135</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>862414</t>
+          <t>861046</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>965794</t>
+          <t>965161</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,47 +6850,47 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
+          <t>30,69%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>1683</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>1785284</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>1709631</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>1859926</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>29,48%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>28,23%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
           <t>30,71%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>1683</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>1785284</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>1714290</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>1857413</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>29,48%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>28,31%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>30,67%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1980540</t>
+          <t>1985736</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2088632</t>
+          <t>2086495</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2178689</t>
+          <t>2179322</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2282069</t>
+          <t>2283437</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,47 +6963,47 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
+          <t>69,31%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>72,62%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>3964</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>4271071</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>4196429</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>4346724</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>70,52%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>69,29%</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>72,57%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>3964</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>4271071</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>4198942</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>4342065</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>70,52%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>69,33%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,77%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>54706</t>
+          <t>53594</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84334</t>
+          <t>84068</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42349</t>
+          <t>42347</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>68352</t>
+          <t>67923</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>103819</t>
+          <t>103222</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>142971</t>
+          <t>143145</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,12%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>160884</t>
+          <t>161150</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>190512</t>
+          <t>191624</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>177982</t>
+          <t>178411</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>203985</t>
+          <t>203987</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>348580</t>
+          <t>348406</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>387732</t>
+          <t>388329</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>79,0%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>97406</t>
+          <t>99582</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>136071</t>
+          <t>137030</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87766</t>
+          <t>86694</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>122548</t>
+          <t>122581</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>199472</t>
+          <t>198198</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>249932</t>
+          <t>251004</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,18%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>227094</t>
+          <t>226135</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>265759</t>
+          <t>263583</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>270779</t>
+          <t>270746</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>305561</t>
+          <t>306633</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>506560</t>
+          <t>505488</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>557020</t>
+          <t>558294</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,8%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65398</t>
+          <t>66963</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>95764</t>
+          <t>96797</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59465</t>
+          <t>59766</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89247</t>
+          <t>89122</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>135254</t>
+          <t>134295</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>176332</t>
+          <t>174241</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,12%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>194743</t>
+          <t>193710</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>225109</t>
+          <t>223544</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>218517</t>
+          <t>218642</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>248299</t>
+          <t>247998</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>421938</t>
+          <t>424029</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>463016</t>
+          <t>463975</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,55%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46973</t>
+          <t>46682</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74295</t>
+          <t>74221</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69053</t>
+          <t>68656</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>104922</t>
+          <t>100839</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>123636</t>
+          <t>124883</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>166116</t>
+          <t>167293</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,64%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>255752</t>
+          <t>255826</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>283074</t>
+          <t>283365</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>243939</t>
+          <t>248022</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>279808</t>
+          <t>280205</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>512792</t>
+          <t>511615</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>555272</t>
+          <t>554025</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,61%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19910</t>
+          <t>20636</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38426</t>
+          <t>39387</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26230</t>
+          <t>25486</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45679</t>
+          <t>45350</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49466</t>
+          <t>49220</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>77175</t>
+          <t>78911</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,81%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>80796</t>
+          <t>79835</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>99312</t>
+          <t>98586</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>99821</t>
+          <t>100150</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>119270</t>
+          <t>120014</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>187547</t>
+          <t>185811</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>215256</t>
+          <t>215502</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,41%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40169</t>
+          <t>40294</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66223</t>
+          <t>66003</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41902</t>
+          <t>41335</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>66569</t>
+          <t>66453</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>87820</t>
+          <t>88512</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>124717</t>
+          <t>124766</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,95%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>167392</t>
+          <t>167612</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>193446</t>
+          <t>193321</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>180568</t>
+          <t>180684</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>205235</t>
+          <t>205802</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>356036</t>
+          <t>355987</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>392933</t>
+          <t>392241</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,59%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>137167</t>
+          <t>136788</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>179736</t>
+          <t>181217</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>140158</t>
+          <t>139741</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>181739</t>
+          <t>180846</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>289606</t>
+          <t>290698</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>348521</t>
+          <t>351468</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,82%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>262571</t>
+          <t>261090</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>305140</t>
+          <t>305519</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>305312</t>
+          <t>306205</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>346893</t>
+          <t>347310</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>580837</t>
+          <t>577890</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>639752</t>
+          <t>638660</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>68,72%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>147318</t>
+          <t>145778</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>192066</t>
+          <t>191112</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>165414</t>
+          <t>165129</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>212512</t>
+          <t>213215</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>323788</t>
+          <t>321657</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>388244</t>
+          <t>390772</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,35%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>448186</t>
+          <t>449140</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>492934</t>
+          <t>494474</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>478829</t>
+          <t>478126</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>525927</t>
+          <t>526212</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>943349</t>
+          <t>940821</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1007805</t>
+          <t>1009936</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,84%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>692520</t>
+          <t>684125</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>783155</t>
+          <t>781855</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>707993</t>
+          <t>707403</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>804134</t>
+          <t>799371</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1416417</t>
+          <t>1423747</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1558872</t>
+          <t>1555652</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,12%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1881178</t>
+          <t>1882478</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1971813</t>
+          <t>1980208</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2063181</t>
+          <t>2067944</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2159322</t>
+          <t>2159912</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3972776</t>
+          <t>3975996</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4115231</t>
+          <t>4107901</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,26%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>44237</t>
+          <t>51533</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31714</t>
+          <t>39100</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60131</t>
+          <t>65863</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>64859</t>
+          <t>75250</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53776</t>
+          <t>61659</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>79821</t>
+          <t>88139</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>109096</t>
+          <t>126783</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>90920</t>
+          <t>107525</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>132590</t>
+          <t>147178</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>261193</t>
+          <t>249384</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>245299</t>
+          <t>235054</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>273716</t>
+          <t>261817</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>222748</t>
+          <t>234214</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>207786</t>
+          <t>221325</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>233831</t>
+          <t>247805</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>483941</t>
+          <t>483598</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>460447</t>
+          <t>463203</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>502117</t>
+          <t>502856</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>82,38%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>305430</t>
+          <t>300917</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>305430</t>
+          <t>300917</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>305430</t>
+          <t>300917</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>287607</t>
+          <t>309464</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>287607</t>
+          <t>309464</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>287607</t>
+          <t>309464</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>593037</t>
+          <t>610381</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>593037</t>
+          <t>610381</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>593037</t>
+          <t>610381</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>139687</t>
+          <t>140121</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>113903</t>
+          <t>116306</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>170626</t>
+          <t>168603</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>109933</t>
+          <t>118313</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>92759</t>
+          <t>101366</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>129753</t>
+          <t>137950</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>249620</t>
+          <t>258433</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>216151</t>
+          <t>226939</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>280441</t>
+          <t>290926</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,72%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>367297</t>
+          <t>377907</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>336358</t>
+          <t>349425</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>393081</t>
+          <t>401722</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>391615</t>
+          <t>413299</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>371795</t>
+          <t>393662</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>408789</t>
+          <t>430246</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>758912</t>
+          <t>791207</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>728091</t>
+          <t>758714</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>792381</t>
+          <t>822701</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,38%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>506984</t>
+          <t>518028</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>506984</t>
+          <t>518028</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>506984</t>
+          <t>518028</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>501548</t>
+          <t>531612</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>501548</t>
+          <t>531612</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>501548</t>
+          <t>531612</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1008532</t>
+          <t>1049640</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1008532</t>
+          <t>1049640</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1008532</t>
+          <t>1049640</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>54138</t>
+          <t>54556</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41162</t>
+          <t>42364</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68359</t>
+          <t>68798</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>47846</t>
+          <t>49416</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38335</t>
+          <t>39563</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59751</t>
+          <t>60451</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>101984</t>
+          <t>103972</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>85812</t>
+          <t>87846</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>120365</t>
+          <t>120405</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>247054</t>
+          <t>245675</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>232833</t>
+          <t>231433</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>260030</t>
+          <t>257867</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>287429</t>
+          <t>292289</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>275524</t>
+          <t>281254</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>296940</t>
+          <t>302142</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>534483</t>
+          <t>537963</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>516102</t>
+          <t>521530</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>550655</t>
+          <t>554089</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,32%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>301192</t>
+          <t>300231</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>301192</t>
+          <t>300231</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>301192</t>
+          <t>300231</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>335275</t>
+          <t>341705</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>335275</t>
+          <t>341705</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>335275</t>
+          <t>341705</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>636467</t>
+          <t>641935</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>636467</t>
+          <t>641935</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>636467</t>
+          <t>641935</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>59092</t>
+          <t>72056</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42432</t>
+          <t>53995</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81789</t>
+          <t>97475</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>101370</t>
+          <t>79687</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58776</t>
+          <t>63697</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>179504</t>
+          <t>100001</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>160463</t>
+          <t>151744</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>117555</t>
+          <t>127767</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>247720</t>
+          <t>184244</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>23,31%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>251028</t>
+          <t>298682</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>228331</t>
+          <t>273263</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>267688</t>
+          <t>316743</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>372095</t>
+          <t>339926</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>293961</t>
+          <t>319612</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>414689</t>
+          <t>355916</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>623122</t>
+          <t>638607</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>535865</t>
+          <t>606107</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>666030</t>
+          <t>662584</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>83,83%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>310120</t>
+          <t>370738</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>310120</t>
+          <t>370738</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>310120</t>
+          <t>370738</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>473465</t>
+          <t>419613</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>473465</t>
+          <t>419613</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>473465</t>
+          <t>419613</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>783585</t>
+          <t>790351</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>783585</t>
+          <t>790351</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>783585</t>
+          <t>790351</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>35951</t>
+          <t>39463</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28176</t>
+          <t>30904</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45685</t>
+          <t>49971</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>45861</t>
+          <t>48156</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38334</t>
+          <t>39801</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53750</t>
+          <t>56786</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>81812</t>
+          <t>87619</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71014</t>
+          <t>74652</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>93870</t>
+          <t>99899</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>24,42%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>132478</t>
+          <t>149836</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>122744</t>
+          <t>139328</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>140253</t>
+          <t>158395</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>156431</t>
+          <t>171646</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>148542</t>
+          <t>163016</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>163958</t>
+          <t>180001</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>288909</t>
+          <t>321482</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>276851</t>
+          <t>309202</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>299707</t>
+          <t>334449</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>81,75%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>168429</t>
+          <t>189299</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>168429</t>
+          <t>189299</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>168429</t>
+          <t>189299</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>202292</t>
+          <t>219802</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>202292</t>
+          <t>219802</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>202292</t>
+          <t>219802</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>370721</t>
+          <t>409101</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>370721</t>
+          <t>409101</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>370721</t>
+          <t>409101</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,22 +12412,22 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>58662</t>
+          <t>58642</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47102</t>
+          <t>46351</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>71132</t>
+          <t>71725</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>39803</t>
+          <t>40516</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30883</t>
+          <t>31652</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49913</t>
+          <t>50263</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>98465</t>
+          <t>99158</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>84036</t>
+          <t>83924</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>115025</t>
+          <t>115638</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,07%</t>
         </is>
       </c>
     </row>
@@ -12525,27 +12525,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>195070</t>
+          <t>191093</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>182600</t>
+          <t>178010</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>206630</t>
+          <t>203384</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>206547</t>
+          <t>211044</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>196437</t>
+          <t>201297</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>215467</t>
+          <t>219908</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>401617</t>
+          <t>402136</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>385057</t>
+          <t>385656</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>416046</t>
+          <t>417370</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,26%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>253732</t>
+          <t>249735</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>253732</t>
+          <t>249735</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>253732</t>
+          <t>249735</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>246350</t>
+          <t>251560</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>246350</t>
+          <t>251560</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>246350</t>
+          <t>251560</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>500082</t>
+          <t>501294</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>500082</t>
+          <t>501294</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>500082</t>
+          <t>501294</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>139599</t>
+          <t>154097</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>115528</t>
+          <t>127584</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>164467</t>
+          <t>182822</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>128721</t>
+          <t>154807</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>59144</t>
+          <t>135795</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>179755</t>
+          <t>175956</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>268320</t>
+          <t>308904</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>165850</t>
+          <t>279653</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>325307</t>
+          <t>345418</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>24,01%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>460096</t>
+          <t>543583</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>435228</t>
+          <t>514858</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>484167</t>
+          <t>570096</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>699001</t>
+          <t>585911</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>647967</t>
+          <t>564762</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>768578</t>
+          <t>604923</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1159097</t>
+          <t>1129494</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1102110</t>
+          <t>1092980</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1261567</t>
+          <t>1158745</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>80,56%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>599695</t>
+          <t>697680</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>599695</t>
+          <t>697680</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>599695</t>
+          <t>697680</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>827722</t>
+          <t>740718</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>827722</t>
+          <t>740718</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>827722</t>
+          <t>740718</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1427417</t>
+          <t>1438398</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1427417</t>
+          <t>1438398</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1427417</t>
+          <t>1438398</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>70323</t>
+          <t>78836</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31160</t>
+          <t>61249</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>102636</t>
+          <t>97840</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>85772</t>
+          <t>97942</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>72228</t>
+          <t>82936</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>99472</t>
+          <t>114576</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>156095</t>
+          <t>176778</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>96851</t>
+          <t>152791</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>190484</t>
+          <t>201384</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>837219</t>
+          <t>691015</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>804906</t>
+          <t>672011</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>876382</t>
+          <t>708602</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>618152</t>
+          <t>712365</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>604452</t>
+          <t>695731</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>631696</t>
+          <t>727371</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1455372</t>
+          <t>1403380</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1420983</t>
+          <t>1378774</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1514616</t>
+          <t>1427367</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>90,33%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>907542</t>
+          <t>769851</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>907542</t>
+          <t>769851</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>907542</t>
+          <t>769851</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>703924</t>
+          <t>810307</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>703924</t>
+          <t>810307</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>703924</t>
+          <t>810307</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1611467</t>
+          <t>1580158</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1611467</t>
+          <t>1580158</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1611467</t>
+          <t>1580158</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>601689</t>
+          <t>649304</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>462873</t>
+          <t>598651</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>672309</t>
+          <t>706277</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>624166</t>
+          <t>664087</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>520003</t>
+          <t>626031</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>711757</t>
+          <t>708473</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1225855</t>
+          <t>1313391</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1075093</t>
+          <t>1248757</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1342961</t>
+          <t>1387336</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2751436</t>
+          <t>2747175</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2680816</t>
+          <t>2690202</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2890252</t>
+          <t>2797828</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2954018</t>
+          <t>2960693</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2866427</t>
+          <t>2916307</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3058181</t>
+          <t>2998749</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5705454</t>
+          <t>5707868</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5588348</t>
+          <t>5633923</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5856216</t>
+          <t>5772502</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>82,21%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3353125</t>
+          <t>3396479</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3353125</t>
+          <t>3396479</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3353125</t>
+          <t>3396479</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3578184</t>
+          <t>3624780</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3578184</t>
+          <t>3624780</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3578184</t>
+          <t>3624780</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>6931309</t>
+          <t>7021259</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6931309</t>
+          <t>7021259</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6931309</t>
+          <t>7021259</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
